--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -92,7 +92,7 @@
 Ergebnissen (Verlaufs-Observations) verknüpft wird.
 Onkologiespezifische Ergänzungen gegenüber MCC:
 - Die Zielart wird über `category` aus `OnkoTherapyGoalTypeVS` codiert (Heilung,
-  Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme).
+  Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt).
 - Über die Extension `onko-therapy-intent` kann zusätzlich die Therapieintention der
   zugehörigen Behandlungslinie hinterlegt werden.
 - `outcomeReference` bindet das Ziel an Verlaufs-Observations (z. B. mCODE
@@ -641,7 +641,7 @@
     <t>Zielart</t>
   </si>
   <si>
-    <t>Art des onkologischen Therapieziels – Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme.</t>
+    <t>Art des onkologischen Therapieziels – Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt.</t>
   </si>
   <si>
     <t>Allows goals to be filtered and sorted.</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3308,7 +3308,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>76</v>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
